--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260730.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260730.xlsx
@@ -601,44 +601,44 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>202608WTX</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>聯詠科技</t>
+          <t>115/08台股期貨</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>9,852,000</t>
+          <t>600</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3.92%</t>
+          <t>3.91%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>202608WTX</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>115/08台股期貨</t>
+          <t>聯詠科技</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>9,852,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>3.82%</t>
+          <t>3.91%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>3.43%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>3.39%</t>
+          <t>3.28%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>3.21%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>3.16%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.04%</t>
+          <t>2.99%</t>
         </is>
       </c>
     </row>
@@ -770,95 +770,95 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.92%</t>
+          <t>2.96%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>旭隼科技</t>
+          <t>中華電信</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>3,801,000</t>
+          <t>24,881,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>2.83%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>中華電信</t>
+          <t>遠傳電信</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>24,881,000</t>
+          <t>33,157,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.83%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>遠傳電信</t>
+          <t>旭隼科技</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>32,918,000</t>
+          <t>3,801,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.73%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>廣達電腦</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>11,037,000</t>
+          <t>30,079,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.69%</t>
+          <t>2.56%</t>
         </is>
       </c>
     </row>
@@ -875,34 +875,34 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>19,313,000</t>
+          <t>19,587,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.58%</t>
+          <t>2.53%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>廣達電腦</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>30,079,000</t>
+          <t>11,165,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>2.52%</t>
         </is>
       </c>
     </row>
@@ -924,51 +924,51 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>2.49%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>祥碩科技</t>
+          <t>技嘉科技</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>2,151,000</t>
+          <t>9,446,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>2.43%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>技嘉科技</t>
+          <t>漢唐集成</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>9,415,000</t>
+          <t>2,820,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>2.30%</t>
         </is>
       </c>
     </row>
@@ -990,51 +990,51 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.30%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>漢唐集成</t>
+          <t>微星科技</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>2,820,000</t>
+          <t>20,683,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.27%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>微星科技</t>
+          <t>祥碩科技</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>20,683,000</t>
+          <t>2,151,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.27%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>2.14%</t>
         </is>
       </c>
     </row>
@@ -1078,29 +1078,29 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>2.08%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>15,056,000</t>
+          <t>2,519,407,937</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>2.04%</t>
         </is>
       </c>
     </row>
@@ -1122,24 +1122,24 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.96%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>英業達股</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>40,734,000</t>
+          <t>17,369,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1166,51 +1166,51 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.89%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>英業達股</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>17,369,000</t>
+          <t>40,734,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.89%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>2,282,973,495</t>
+          <t>15,056,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.86%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.78%</t>
         </is>
       </c>
     </row>
@@ -1254,24 +1254,24 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>順達科技</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>6,546,000</t>
+          <t>1,971,505,322</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,39 +1283,39 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>新普科技</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>518,000</t>
+          <t>5,666,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.59%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>1,976,545,322</t>
+          <t>518,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,22 +1327,22 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>新普科技</t>
+          <t>順達科技</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>5,666,000</t>
+          <t>6,546,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.51%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.50%</t>
         </is>
       </c>
     </row>
@@ -1386,73 +1386,73 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.49%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>精成科技</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>23,205,000</t>
+          <t>16,505,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.47%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>至上電子</t>
+          <t>精成科技</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>22,613,000</t>
+          <t>23,205,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.45%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>至上電子</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>16,505,000</t>
+          <t>22,613,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.38%</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.35%</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.26%</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
@@ -1584,51 +1584,51 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>牧德科技</t>
+          <t>可寧衛股</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>2,088,000</t>
+          <t>48,929,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>可寧衛股</t>
+          <t>牧德科技</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>48,929,000</t>
+          <t>2,088,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
@@ -1650,95 +1650,95 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>日電貿股</t>
+          <t>長華科技</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>8,865,000</t>
+          <t>18,691,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>長華科技</t>
+          <t>致伸科技</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>18,691,000</t>
+          <t>17,282,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>致伸科技</t>
+          <t>瀚宇博德</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>17,282,000</t>
+          <t>16,588,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>瀚宇博德</t>
+          <t>日電貿股</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>16,588,000</t>
+          <t>8,865,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>-37,677,105</t>
+          <t>-18,301,118</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
     </row>
